--- a/resources/data-imports/Monsters/labyrinth-raid-monsters.xlsx
+++ b/resources/data-imports/Monsters/labyrinth-raid-monsters.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
@@ -370,19 +370,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -406,37 +406,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -512,164 +512,164 @@
   <dimension ref="A1:AX15"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="39" style="0" width="19.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="39" style="1" width="19.33"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="Z1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AA1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AB1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AC1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AD1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AE1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AF1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AG1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AH1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AI1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AJ1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AK1" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AL1" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="0" t="s">
+      <c r="AM1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AN1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AO1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AP1" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AQ1" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AR1" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AS1" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AT1" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AU1" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="AV1" s="1" t="s">
+      <c r="AV1" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="AW1" s="1" t="s">
+      <c r="AW1" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AX1" s="1" t="s">
+      <c r="AX1" s="2" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2" t="s">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1" t="s">
         <v>50</v>
       </c>
       <c r="C2" s="3" t="n">
@@ -696,50 +696,50 @@
       <c r="J2" s="3" t="n">
         <v>25055700.0395915</v>
       </c>
-      <c r="K2" s="2" t="n">
+      <c r="K2" s="1" t="n">
         <v>0.40258593375875</v>
       </c>
-      <c r="L2" s="2" t="n">
+      <c r="L2" s="1" t="n">
         <v>0.40258593375875</v>
       </c>
-      <c r="M2" s="2" t="n">
+      <c r="M2" s="1" t="n">
         <v>0.40258593375875</v>
       </c>
-      <c r="N2" s="2" t="n">
+      <c r="N2" s="1" t="n">
         <v>0.40258593375875</v>
       </c>
-      <c r="O2" s="2"/>
-      <c r="P2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="S2" s="2" t="n">
+      <c r="O2" s="1"/>
+      <c r="P2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S2" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T2" s="2" t="s">
+      <c r="T2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="U2" s="3" t="n">
         <v>33.983909703184</v>
       </c>
-      <c r="V2" s="2" t="n">
+      <c r="V2" s="1" t="n">
         <v>0.046079652675</v>
       </c>
       <c r="W2" s="3" t="n">
-        <v>348201663.24165</v>
-      </c>
-      <c r="X2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" s="2" t="s">
+        <v>500000</v>
+      </c>
+      <c r="X2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="Z2" s="2" t="s">
+      <c r="Z2" s="1" t="s">
         <v>51</v>
       </c>
       <c r="AA2" s="3" t="n">
@@ -748,70 +748,70 @@
       <c r="AB2" s="3" t="n">
         <v>25055700.0395915</v>
       </c>
-      <c r="AC2" s="2" t="n">
+      <c r="AC2" s="1" t="n">
         <v>0.40258593375875</v>
       </c>
-      <c r="AD2" s="2" t="n">
+      <c r="AD2" s="1" t="n">
         <v>0.40258593375875</v>
       </c>
-      <c r="AE2" s="2" t="n">
+      <c r="AE2" s="1" t="n">
         <v>0.40258593375875</v>
       </c>
-      <c r="AF2" s="2" t="n">
+      <c r="AF2" s="1" t="n">
         <v>0.40258593375875</v>
       </c>
-      <c r="AG2" s="2" t="n">
+      <c r="AG2" s="1" t="n">
         <v>0.238543427806562</v>
       </c>
-      <c r="AH2" s="2" t="n">
+      <c r="AH2" s="1" t="n">
         <v>0.238543427806562</v>
       </c>
-      <c r="AI2" s="2" t="n">
+      <c r="AI2" s="1" t="n">
         <v>0.2406045773952</v>
       </c>
-      <c r="AJ2" s="2" t="n">
+      <c r="AJ2" s="1" t="n">
         <v>0.2406045773952</v>
       </c>
-      <c r="AK2" s="2" t="n">
+      <c r="AK2" s="1" t="n">
         <v>0.2406045773952</v>
       </c>
-      <c r="AL2" s="2" t="n">
+      <c r="AL2" s="1" t="n">
         <v>0.2406045773952</v>
       </c>
-      <c r="AM2" s="0" t="s">
+      <c r="AM2" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="AN2" s="2" t="n">
+      <c r="AN2" s="1" t="n">
         <v>0.03</v>
       </c>
-      <c r="AO2" s="2" t="s">
+      <c r="AO2" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="AP2" s="2"/>
-      <c r="AQ2" s="2" t="n">
+      <c r="AP2" s="1"/>
+      <c r="AQ2" s="1" t="n">
         <v>0.00184784955034969</v>
       </c>
-      <c r="AR2" s="2" t="n">
+      <c r="AR2" s="1" t="n">
         <v>0.0386345406344547</v>
       </c>
-      <c r="AS2" s="2" t="n">
+      <c r="AS2" s="1" t="n">
         <v>0.0696403317041922</v>
       </c>
-      <c r="AT2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU2" s="2"/>
-      <c r="AV2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW2" s="2" t="n">
+      <c r="AT2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU2" s="1"/>
+      <c r="AV2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW2" s="1" t="n">
         <v>0.21361125161538</v>
       </c>
-      <c r="AX2" s="2"/>
+      <c r="AX2" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2" t="s">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1" t="s">
         <v>54</v>
       </c>
       <c r="C3" s="3" t="n">
@@ -838,50 +838,50 @@
       <c r="J3" s="3" t="n">
         <v>36205053.093599</v>
       </c>
-      <c r="K3" s="2" t="n">
+      <c r="K3" s="1" t="n">
         <v>0.431771401026591</v>
       </c>
-      <c r="L3" s="2" t="n">
+      <c r="L3" s="1" t="n">
         <v>0.431771401026591</v>
       </c>
-      <c r="M3" s="2" t="n">
+      <c r="M3" s="1" t="n">
         <v>0.431771401026591</v>
       </c>
-      <c r="N3" s="2" t="n">
+      <c r="N3" s="1" t="n">
         <v>0.431771401026591</v>
       </c>
-      <c r="O3" s="2"/>
-      <c r="P3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="S3" s="2" t="n">
+      <c r="O3" s="1"/>
+      <c r="P3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T3" s="2" t="s">
+      <c r="T3" s="1" t="s">
         <v>3</v>
       </c>
       <c r="U3" s="3" t="n">
         <v>39.6223296912419</v>
       </c>
-      <c r="V3" s="2" t="n">
+      <c r="V3" s="1" t="n">
         <v>0.0571088175427612</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>410937957.07532</v>
-      </c>
-      <c r="X3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" s="2" t="s">
+        <v>693267</v>
+      </c>
+      <c r="X3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="Z3" s="2" t="s">
+      <c r="Z3" s="1" t="s">
         <v>55</v>
       </c>
       <c r="AA3" s="3" t="n">
@@ -890,64 +890,64 @@
       <c r="AB3" s="3" t="n">
         <v>36205053.093599</v>
       </c>
-      <c r="AC3" s="2" t="n">
+      <c r="AC3" s="1" t="n">
         <v>0.431771401026591</v>
       </c>
-      <c r="AD3" s="2" t="n">
+      <c r="AD3" s="1" t="n">
         <v>0.431771401026591</v>
       </c>
-      <c r="AE3" s="2" t="n">
+      <c r="AE3" s="1" t="n">
         <v>0.431771401026591</v>
       </c>
-      <c r="AF3" s="2" t="n">
+      <c r="AF3" s="1" t="n">
         <v>0.431771401026591</v>
       </c>
-      <c r="AG3" s="2" t="n">
+      <c r="AG3" s="1" t="n">
         <v>0.260517070348049</v>
       </c>
-      <c r="AH3" s="2" t="n">
+      <c r="AH3" s="1" t="n">
         <v>0.260517070348049</v>
       </c>
-      <c r="AI3" s="2" t="n">
+      <c r="AI3" s="1" t="n">
         <v>0.263900874996913</v>
       </c>
-      <c r="AJ3" s="2" t="n">
+      <c r="AJ3" s="1" t="n">
         <v>0.263900874996913</v>
       </c>
-      <c r="AK3" s="2" t="n">
+      <c r="AK3" s="1" t="n">
         <v>0.263900874996913</v>
       </c>
-      <c r="AL3" s="2" t="n">
+      <c r="AL3" s="1" t="n">
         <v>0.263900874996913</v>
       </c>
-      <c r="AO3" s="2" t="s">
+      <c r="AO3" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="AP3" s="2"/>
-      <c r="AQ3" s="2" t="n">
+      <c r="AP3" s="1"/>
+      <c r="AQ3" s="1" t="n">
         <v>0.00251188592772002</v>
       </c>
-      <c r="AR3" s="2" t="n">
+      <c r="AR3" s="1" t="n">
         <v>0.0438432764469703</v>
       </c>
-      <c r="AS3" s="2" t="n">
+      <c r="AS3" s="1" t="n">
         <v>0.0821875897436961</v>
       </c>
-      <c r="AT3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU3" s="2"/>
-      <c r="AV3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" s="2" t="n">
+      <c r="AT3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU3" s="1"/>
+      <c r="AV3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW3" s="1" t="n">
         <v>0.232701902783498</v>
       </c>
-      <c r="AX3" s="2"/>
+      <c r="AX3" s="1"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2" t="s">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1" t="s">
         <v>56</v>
       </c>
       <c r="C4" s="3" t="n">
@@ -974,50 +974,50 @@
       <c r="J4" s="3" t="n">
         <v>52315675.372832</v>
       </c>
-      <c r="K4" s="2" t="n">
+      <c r="K4" s="1" t="n">
         <v>0.463072668744013</v>
       </c>
-      <c r="L4" s="2" t="n">
+      <c r="L4" s="1" t="n">
         <v>0.463072668744013</v>
       </c>
-      <c r="M4" s="2" t="n">
+      <c r="M4" s="1" t="n">
         <v>0.463072668744013</v>
       </c>
-      <c r="N4" s="2" t="n">
+      <c r="N4" s="1" t="n">
         <v>0.463072668744013</v>
       </c>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="S4" s="2" t="n">
+      <c r="O4" s="1"/>
+      <c r="P4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T4" s="2" t="s">
+      <c r="T4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="U4" s="3" t="n">
         <v>46.1962447485665</v>
       </c>
-      <c r="V4" s="2" t="n">
+      <c r="V4" s="1" t="n">
         <v>0.0707778130216211</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>484977593.137006</v>
-      </c>
-      <c r="X4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="2" t="s">
+        <v>961239</v>
+      </c>
+      <c r="X4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="Z4" s="2" t="s">
+      <c r="Z4" s="1" t="s">
         <v>57</v>
       </c>
       <c r="AA4" s="3" t="n">
@@ -1026,64 +1026,64 @@
       <c r="AB4" s="3" t="n">
         <v>52315675.372832</v>
       </c>
-      <c r="AC4" s="2" t="n">
+      <c r="AC4" s="1" t="n">
         <v>0.463072668744013</v>
       </c>
-      <c r="AD4" s="2" t="n">
+      <c r="AD4" s="1" t="n">
         <v>0.463072668744013</v>
       </c>
-      <c r="AE4" s="2" t="n">
+      <c r="AE4" s="1" t="n">
         <v>0.463072668744013</v>
       </c>
-      <c r="AF4" s="2" t="n">
+      <c r="AF4" s="1" t="n">
         <v>0.463072668744013</v>
       </c>
-      <c r="AG4" s="2" t="n">
+      <c r="AG4" s="1" t="n">
         <v>0.284514834748522</v>
       </c>
-      <c r="AH4" s="2" t="n">
+      <c r="AH4" s="1" t="n">
         <v>0.284514834748522</v>
       </c>
-      <c r="AI4" s="2" t="n">
+      <c r="AI4" s="1" t="n">
         <v>0.289452813317614</v>
       </c>
-      <c r="AJ4" s="2" t="n">
+      <c r="AJ4" s="1" t="n">
         <v>0.289452813317614</v>
       </c>
-      <c r="AK4" s="2" t="n">
+      <c r="AK4" s="1" t="n">
         <v>0.289452813317614</v>
       </c>
-      <c r="AL4" s="2" t="n">
+      <c r="AL4" s="1" t="n">
         <v>0.289452813317614</v>
       </c>
-      <c r="AO4" s="2" t="s">
+      <c r="AO4" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="AP4" s="2"/>
-      <c r="AQ4" s="2" t="n">
+      <c r="AP4" s="1"/>
+      <c r="AQ4" s="1" t="n">
         <v>0.00341454796072755</v>
       </c>
-      <c r="AR4" s="2" t="n">
+      <c r="AR4" s="1" t="n">
         <v>0.0497542576678444</v>
       </c>
-      <c r="AS4" s="2" t="n">
+      <c r="AS4" s="1" t="n">
         <v>0.0969955159973984</v>
       </c>
-      <c r="AT4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU4" s="2"/>
-      <c r="AV4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW4" s="2" t="n">
+      <c r="AT4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU4" s="1"/>
+      <c r="AV4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" s="1" t="n">
         <v>0.253498704537162</v>
       </c>
-      <c r="AX4" s="2"/>
+      <c r="AX4" s="1"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2" t="s">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1" t="s">
         <v>58</v>
       </c>
       <c r="C5" s="3" t="n">
@@ -1110,50 +1110,50 @@
       <c r="J5" s="3" t="n">
         <v>75595245.8525583</v>
       </c>
-      <c r="K5" s="2" t="n">
+      <c r="K5" s="1" t="n">
         <v>0.49664312186461</v>
       </c>
-      <c r="L5" s="2" t="n">
+      <c r="L5" s="1" t="n">
         <v>0.49664312186461</v>
       </c>
-      <c r="M5" s="2" t="n">
+      <c r="M5" s="1" t="n">
         <v>0.49664312186461</v>
       </c>
-      <c r="N5" s="2" t="n">
+      <c r="N5" s="1" t="n">
         <v>0.49664312186461</v>
       </c>
-      <c r="O5" s="2"/>
-      <c r="P5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" s="2" t="n">
+      <c r="O5" s="1"/>
+      <c r="P5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T5" s="2" t="s">
+      <c r="T5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="U5" s="3" t="n">
         <v>53.8608669782781</v>
       </c>
-      <c r="V5" s="2" t="n">
+      <c r="V5" s="1" t="n">
         <v>0.0877184825683462</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>572357120.57101</v>
-      </c>
-      <c r="X5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="2" t="s">
+        <v>1332790</v>
+      </c>
+      <c r="X5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="Z5" s="2" t="s">
+      <c r="Z5" s="1" t="s">
         <v>59</v>
       </c>
       <c r="AA5" s="3" t="n">
@@ -1162,70 +1162,70 @@
       <c r="AB5" s="3" t="n">
         <v>75595245.8525583</v>
       </c>
-      <c r="AC5" s="2" t="n">
+      <c r="AC5" s="1" t="n">
         <v>0.49664312186461</v>
       </c>
-      <c r="AD5" s="2" t="n">
+      <c r="AD5" s="1" t="n">
         <v>0.49664312186461</v>
       </c>
-      <c r="AE5" s="2" t="n">
+      <c r="AE5" s="1" t="n">
         <v>0.49664312186461</v>
       </c>
-      <c r="AF5" s="2" t="n">
+      <c r="AF5" s="1" t="n">
         <v>0.49664312186461</v>
       </c>
-      <c r="AG5" s="2" t="n">
+      <c r="AG5" s="1" t="n">
         <v>0.310723174814734</v>
       </c>
-      <c r="AH5" s="2" t="n">
+      <c r="AH5" s="1" t="n">
         <v>0.310723174814734</v>
       </c>
-      <c r="AI5" s="2" t="n">
+      <c r="AI5" s="1" t="n">
         <v>0.317478792514279</v>
       </c>
-      <c r="AJ5" s="2" t="n">
+      <c r="AJ5" s="1" t="n">
         <v>0.317478792514279</v>
       </c>
-      <c r="AK5" s="2" t="n">
+      <c r="AK5" s="1" t="n">
         <v>0.317478792514279</v>
       </c>
-      <c r="AL5" s="2" t="n">
+      <c r="AL5" s="1" t="n">
         <v>0.317478792514279</v>
       </c>
-      <c r="AM5" s="0" t="s">
+      <c r="AM5" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="AN5" s="0" t="n">
+      <c r="AN5" s="1" t="n">
         <v>0.08</v>
       </c>
-      <c r="AO5" s="2" t="s">
+      <c r="AO5" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="AP5" s="2"/>
-      <c r="AQ5" s="2" t="n">
+      <c r="AP5" s="1"/>
+      <c r="AQ5" s="1" t="n">
         <v>0.00464158728206715</v>
       </c>
-      <c r="AR5" s="2" t="n">
+      <c r="AR5" s="1" t="n">
         <v>0.0564621615146035</v>
       </c>
-      <c r="AS5" s="2" t="n">
+      <c r="AS5" s="1" t="n">
         <v>0.114471420234381</v>
       </c>
-      <c r="AT5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU5" s="2"/>
-      <c r="AV5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW5" s="2" t="n">
+      <c r="AT5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU5" s="1"/>
+      <c r="AV5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" s="1" t="n">
         <v>0.276154137260353</v>
       </c>
-      <c r="AX5" s="2"/>
+      <c r="AX5" s="1"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2" t="s">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1" t="s">
         <v>61</v>
       </c>
       <c r="C6" s="3" t="n">
@@ -1252,50 +1252,50 @@
       <c r="J6" s="3" t="n">
         <v>109233822.459194</v>
       </c>
-      <c r="K6" s="2" t="n">
+      <c r="K6" s="1" t="n">
         <v>0.532647264984185</v>
       </c>
-      <c r="L6" s="2" t="n">
+      <c r="L6" s="1" t="n">
         <v>0.532647264984185</v>
       </c>
-      <c r="M6" s="2" t="n">
+      <c r="M6" s="1" t="n">
         <v>0.532647264984185</v>
       </c>
-      <c r="N6" s="2" t="n">
+      <c r="N6" s="1" t="n">
         <v>0.532647264984185</v>
       </c>
-      <c r="O6" s="2"/>
-      <c r="P6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" s="2" t="n">
+      <c r="O6" s="1"/>
+      <c r="P6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T6" s="2" t="s">
+      <c r="T6" s="1" t="s">
         <v>6</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>62.7971604064589</v>
       </c>
-      <c r="V6" s="2" t="n">
+      <c r="V6" s="1" t="n">
         <v>0.10871390137108</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>675480018.260952</v>
-      </c>
-      <c r="X6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="2" t="s">
+        <v>1847960</v>
+      </c>
+      <c r="X6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="Z6" s="2" t="s">
+      <c r="Z6" s="1" t="s">
         <v>62</v>
       </c>
       <c r="AA6" s="3" t="n">
@@ -1304,65 +1304,64 @@
       <c r="AB6" s="3" t="n">
         <v>109233822.459194</v>
       </c>
-      <c r="AC6" s="2" t="n">
+      <c r="AC6" s="1" t="n">
         <v>0.532647264984185</v>
       </c>
-      <c r="AD6" s="2" t="n">
+      <c r="AD6" s="1" t="n">
         <v>0.532647264984185</v>
       </c>
-      <c r="AE6" s="2" t="n">
+      <c r="AE6" s="1" t="n">
         <v>0.532647264984185</v>
       </c>
-      <c r="AF6" s="2" t="n">
+      <c r="AF6" s="1" t="n">
         <v>0.532647264984185</v>
       </c>
-      <c r="AG6" s="2" t="n">
+      <c r="AG6" s="1" t="n">
         <v>0.33934571971365</v>
       </c>
-      <c r="AH6" s="2" t="n">
+      <c r="AH6" s="1" t="n">
         <v>0.33934571971365</v>
       </c>
-      <c r="AI6" s="2" t="n">
+      <c r="AI6" s="1" t="n">
         <v>0.348218359120681</v>
       </c>
-      <c r="AJ6" s="2" t="n">
+      <c r="AJ6" s="1" t="n">
         <v>0.348218359120681</v>
       </c>
-      <c r="AK6" s="2" t="n">
+      <c r="AK6" s="1" t="n">
         <v>0.348218359120681</v>
       </c>
-      <c r="AL6" s="2" t="n">
+      <c r="AL6" s="1" t="n">
         <v>0.348218359120681</v>
       </c>
-      <c r="AM6" s="2"/>
-      <c r="AO6" s="2" t="s">
+      <c r="AO6" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="AP6" s="2"/>
-      <c r="AQ6" s="2" t="n">
+      <c r="AP6" s="1"/>
+      <c r="AQ6" s="1" t="n">
         <v>0.00630957091387786</v>
       </c>
-      <c r="AR6" s="2" t="n">
+      <c r="AR6" s="1" t="n">
         <v>0.0640744296535154</v>
       </c>
-      <c r="AS6" s="2" t="n">
+      <c r="AS6" s="1" t="n">
         <v>0.135095998157562</v>
       </c>
-      <c r="AT6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU6" s="2"/>
-      <c r="AV6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW6" s="2" t="n">
+      <c r="AT6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU6" s="1"/>
+      <c r="AV6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" s="1" t="n">
         <v>0.300834308661448</v>
       </c>
-      <c r="AX6" s="2"/>
+      <c r="AX6" s="1"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2" t="s">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1" t="s">
         <v>63</v>
       </c>
       <c r="C7" s="3" t="n">
@@ -1389,50 +1388,50 @@
       <c r="J7" s="3" t="n">
         <v>157840983.708406</v>
       </c>
-      <c r="K7" s="2" t="n">
+      <c r="K7" s="1" t="n">
         <v>0.571261528459214</v>
       </c>
-      <c r="L7" s="2" t="n">
+      <c r="L7" s="1" t="n">
         <v>0.571261528459214</v>
       </c>
-      <c r="M7" s="2" t="n">
+      <c r="M7" s="1" t="n">
         <v>0.571261528459214</v>
       </c>
-      <c r="N7" s="2" t="n">
+      <c r="N7" s="1" t="n">
         <v>0.571261528459214</v>
       </c>
-      <c r="O7" s="2"/>
-      <c r="P7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" s="2" t="n">
+      <c r="O7" s="1"/>
+      <c r="P7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T7" s="2" t="s">
+      <c r="T7" s="1" t="s">
         <v>4</v>
       </c>
       <c r="U7" s="3" t="n">
         <v>73.2161135970003</v>
       </c>
-      <c r="V7" s="2" t="n">
+      <c r="V7" s="1" t="n">
         <v>0.134734573664248</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>797182805.404109</v>
-      </c>
-      <c r="X7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="2" t="s">
+        <v>2562259</v>
+      </c>
+      <c r="X7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="Z7" s="2" t="s">
+      <c r="Z7" s="1" t="s">
         <v>64</v>
       </c>
       <c r="AA7" s="3" t="n">
@@ -1441,65 +1440,64 @@
       <c r="AB7" s="3" t="n">
         <v>157840983.708406</v>
       </c>
-      <c r="AC7" s="2" t="n">
+      <c r="AC7" s="1" t="n">
         <v>0.571261528459214</v>
       </c>
-      <c r="AD7" s="2" t="n">
+      <c r="AD7" s="1" t="n">
         <v>0.571261528459214</v>
       </c>
-      <c r="AE7" s="2" t="n">
+      <c r="AE7" s="1" t="n">
         <v>0.571261528459214</v>
       </c>
-      <c r="AF7" s="2" t="n">
+      <c r="AF7" s="1" t="n">
         <v>0.571261528459214</v>
       </c>
-      <c r="AG7" s="2" t="n">
+      <c r="AG7" s="1" t="n">
         <v>0.370604856096221</v>
       </c>
-      <c r="AH7" s="2" t="n">
+      <c r="AH7" s="1" t="n">
         <v>0.370604856096221</v>
       </c>
-      <c r="AI7" s="2" t="n">
+      <c r="AI7" s="1" t="n">
         <v>0.381934253524182</v>
       </c>
-      <c r="AJ7" s="2" t="n">
+      <c r="AJ7" s="1" t="n">
         <v>0.381934253524182</v>
       </c>
-      <c r="AK7" s="2" t="n">
+      <c r="AK7" s="1" t="n">
         <v>0.381934253524182</v>
       </c>
-      <c r="AL7" s="2" t="n">
+      <c r="AL7" s="1" t="n">
         <v>0.381934253524182</v>
       </c>
-      <c r="AM7" s="2"/>
-      <c r="AO7" s="2" t="s">
+      <c r="AO7" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="AP7" s="2"/>
-      <c r="AQ7" s="2" t="n">
+      <c r="AP7" s="1"/>
+      <c r="AQ7" s="1" t="n">
         <v>0.00857695497207662</v>
       </c>
-      <c r="AR7" s="2" t="n">
+      <c r="AR7" s="1" t="n">
         <v>0.0727129891115031</v>
       </c>
-      <c r="AS7" s="2" t="n">
+      <c r="AS7" s="1" t="n">
         <v>0.159436553515446</v>
       </c>
-      <c r="AT7" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU7" s="2"/>
-      <c r="AV7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW7" s="2" t="n">
+      <c r="AT7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU7" s="1"/>
+      <c r="AV7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" s="1" t="n">
         <v>0.32772017166083</v>
       </c>
-      <c r="AX7" s="2"/>
+      <c r="AX7" s="1"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2" t="s">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1" t="s">
         <v>65</v>
       </c>
       <c r="C8" s="3" t="n">
@@ -1526,50 +1524,50 @@
       <c r="J8" s="3" t="n">
         <v>228077490.809629</v>
       </c>
-      <c r="K8" s="2" t="n">
+      <c r="K8" s="1" t="n">
         <v>0.612675132964865</v>
       </c>
-      <c r="L8" s="2" t="n">
+      <c r="L8" s="1" t="n">
         <v>0.612675132964865</v>
       </c>
-      <c r="M8" s="2" t="n">
+      <c r="M8" s="1" t="n">
         <v>0.612675132964865</v>
       </c>
-      <c r="N8" s="2" t="n">
+      <c r="N8" s="1" t="n">
         <v>0.612675132964865</v>
       </c>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" s="2" t="n">
+      <c r="O8" s="1"/>
+      <c r="P8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T8" s="2" t="s">
+      <c r="T8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="U8" s="3" t="n">
         <v>85.3637211547784</v>
       </c>
-      <c r="V8" s="2" t="n">
+      <c r="V8" s="1" t="n">
         <v>0.166983293870785</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>940813063.379854</v>
-      </c>
-      <c r="X8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="2" t="s">
+        <v>3552661</v>
+      </c>
+      <c r="X8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="Z8" s="2" t="s">
+      <c r="Z8" s="1" t="s">
         <v>66</v>
       </c>
       <c r="AA8" s="3" t="n">
@@ -1578,65 +1576,64 @@
       <c r="AB8" s="3" t="n">
         <v>228077490.809629</v>
       </c>
-      <c r="AC8" s="2" t="n">
+      <c r="AC8" s="1" t="n">
         <v>0.612675132964865</v>
       </c>
-      <c r="AD8" s="2" t="n">
+      <c r="AD8" s="1" t="n">
         <v>0.612675132964865</v>
       </c>
-      <c r="AE8" s="2" t="n">
+      <c r="AE8" s="1" t="n">
         <v>0.612675132964865</v>
       </c>
-      <c r="AF8" s="2" t="n">
+      <c r="AF8" s="1" t="n">
         <v>0.612675132964865</v>
       </c>
-      <c r="AG8" s="2" t="n">
+      <c r="AG8" s="1" t="n">
         <v>0.404743455959895</v>
       </c>
-      <c r="AH8" s="2" t="n">
+      <c r="AH8" s="1" t="n">
         <v>0.404743455959895</v>
       </c>
-      <c r="AI8" s="2" t="n">
+      <c r="AI8" s="1" t="n">
         <v>0.418914655687407</v>
       </c>
-      <c r="AJ8" s="2" t="n">
+      <c r="AJ8" s="1" t="n">
         <v>0.418914655687407</v>
       </c>
-      <c r="AK8" s="2" t="n">
+      <c r="AK8" s="1" t="n">
         <v>0.418914655687407</v>
       </c>
-      <c r="AL8" s="2" t="n">
+      <c r="AL8" s="1" t="n">
         <v>0.418914655687407</v>
       </c>
-      <c r="AM8" s="2"/>
-      <c r="AO8" s="2" t="s">
+      <c r="AO8" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="AP8" s="2"/>
-      <c r="AQ8" s="2" t="n">
+      <c r="AP8" s="1"/>
+      <c r="AQ8" s="1" t="n">
         <v>0.0116591377761087</v>
       </c>
-      <c r="AR8" s="2" t="n">
+      <c r="AR8" s="1" t="n">
         <v>0.0825162052026083</v>
       </c>
-      <c r="AS8" s="2" t="n">
+      <c r="AS8" s="1" t="n">
         <v>0.188162602472031</v>
       </c>
-      <c r="AT8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU8" s="2"/>
-      <c r="AV8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW8" s="2" t="n">
+      <c r="AT8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU8" s="1"/>
+      <c r="AV8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" s="1" t="n">
         <v>0.35700885112233</v>
       </c>
-      <c r="AX8" s="2"/>
+      <c r="AX8" s="1"/>
     </row>
     <row r="9" customFormat="false" ht="16.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2" t="s">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1" t="s">
         <v>67</v>
       </c>
       <c r="C9" s="3" t="n">
@@ -1663,50 +1660,50 @@
       <c r="J9" s="3" t="n">
         <v>329568028.479322</v>
       </c>
-      <c r="K9" s="2" t="n">
+      <c r="K9" s="1" t="n">
         <v>0.657091016729152</v>
       </c>
-      <c r="L9" s="2" t="n">
+      <c r="L9" s="1" t="n">
         <v>0.657091016729152</v>
       </c>
-      <c r="M9" s="2" t="n">
+      <c r="M9" s="1" t="n">
         <v>0.657091016729152</v>
       </c>
-      <c r="N9" s="2" t="n">
+      <c r="N9" s="1" t="n">
         <v>0.657091016729152</v>
       </c>
-      <c r="O9" s="2"/>
-      <c r="P9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" s="2" t="n">
+      <c r="O9" s="1"/>
+      <c r="P9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T9" s="2" t="s">
+      <c r="T9" s="1" t="s">
         <v>2</v>
       </c>
       <c r="U9" s="3" t="n">
         <v>99.5267917319408</v>
       </c>
-      <c r="V9" s="2" t="n">
+      <c r="V9" s="1" t="n">
         <v>0.206950745258758</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>1110321514.99742</v>
-      </c>
-      <c r="X9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="2" t="s">
+        <v>4925886</v>
+      </c>
+      <c r="X9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="Z9" s="2" t="s">
+      <c r="Z9" s="1" t="s">
         <v>68</v>
       </c>
       <c r="AA9" s="3" t="n">
@@ -1715,70 +1712,70 @@
       <c r="AB9" s="3" t="n">
         <v>329568028.479322</v>
       </c>
-      <c r="AC9" s="2" t="n">
+      <c r="AC9" s="1" t="n">
         <v>0.657091016729152</v>
       </c>
-      <c r="AD9" s="2" t="n">
+      <c r="AD9" s="1" t="n">
         <v>0.657091016729152</v>
       </c>
-      <c r="AE9" s="2" t="n">
+      <c r="AE9" s="1" t="n">
         <v>0.657091016729152</v>
       </c>
-      <c r="AF9" s="2" t="n">
+      <c r="AF9" s="1" t="n">
         <v>0.657091016729152</v>
       </c>
-      <c r="AG9" s="2" t="n">
+      <c r="AG9" s="1" t="n">
         <v>0.442026763674751</v>
       </c>
-      <c r="AH9" s="2" t="n">
+      <c r="AH9" s="1" t="n">
         <v>0.442026763674751</v>
       </c>
-      <c r="AI9" s="2" t="n">
+      <c r="AI9" s="1" t="n">
         <v>0.459475648309685</v>
       </c>
-      <c r="AJ9" s="2" t="n">
+      <c r="AJ9" s="1" t="n">
         <v>0.459475648309685</v>
       </c>
-      <c r="AK9" s="2" t="n">
+      <c r="AK9" s="1" t="n">
         <v>0.459475648309685</v>
       </c>
-      <c r="AL9" s="2" t="n">
+      <c r="AL9" s="1" t="n">
         <v>0.459475648309685</v>
       </c>
-      <c r="AM9" s="0" t="s">
+      <c r="AM9" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="AN9" s="0" t="n">
+      <c r="AN9" s="1" t="n">
         <v>0.12</v>
       </c>
-      <c r="AO9" s="2" t="s">
+      <c r="AO9" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="AP9" s="2"/>
-      <c r="AQ9" s="2" t="n">
+      <c r="AP9" s="1"/>
+      <c r="AQ9" s="1" t="n">
         <v>0.0158489223885213</v>
       </c>
-      <c r="AR9" s="2" t="n">
+      <c r="AR9" s="1" t="n">
         <v>0.0936410977493676</v>
       </c>
-      <c r="AS9" s="2" t="n">
+      <c r="AS9" s="1" t="n">
         <v>0.222064289451777</v>
       </c>
-      <c r="AT9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU9" s="2"/>
-      <c r="AV9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW9" s="2" t="n">
+      <c r="AT9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU9" s="1"/>
+      <c r="AV9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" s="1" t="n">
         <v>0.388915089155984</v>
       </c>
-      <c r="AX9" s="2"/>
+      <c r="AX9" s="1"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2" t="s">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1" t="s">
         <v>70</v>
       </c>
       <c r="C10" s="3" t="n">
@@ -1805,50 +1802,50 @@
       <c r="J10" s="3" t="n">
         <v>476220099.625728</v>
       </c>
-      <c r="K10" s="2" t="n">
+      <c r="K10" s="1" t="n">
         <v>0.704726829986932</v>
       </c>
-      <c r="L10" s="2" t="n">
+      <c r="L10" s="1" t="n">
         <v>0.704726829986932</v>
       </c>
-      <c r="M10" s="2" t="n">
+      <c r="M10" s="1" t="n">
         <v>0.704726829986932</v>
       </c>
-      <c r="N10" s="2" t="n">
+      <c r="N10" s="1" t="n">
         <v>0.704726829986932</v>
       </c>
-      <c r="O10" s="2"/>
-      <c r="P10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" s="2" t="n">
+      <c r="O10" s="1"/>
+      <c r="P10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T10" s="2" t="s">
+      <c r="T10" s="1" t="s">
         <v>2</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>116.039719666071</v>
       </c>
-      <c r="V10" s="2" t="n">
+      <c r="V10" s="1" t="n">
         <v>0.256484406136442</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>1310370693.87335</v>
-      </c>
-      <c r="X10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="2" t="s">
+        <v>6829909</v>
+      </c>
+      <c r="X10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="Z10" s="2" t="s">
+      <c r="Z10" s="1" t="s">
         <v>71</v>
       </c>
       <c r="AA10" s="3" t="n">
@@ -1857,65 +1854,64 @@
       <c r="AB10" s="3" t="n">
         <v>476220099.625728</v>
       </c>
-      <c r="AC10" s="2" t="n">
+      <c r="AC10" s="1" t="n">
         <v>0.704726829986932</v>
       </c>
-      <c r="AD10" s="2" t="n">
+      <c r="AD10" s="1" t="n">
         <v>0.704726829986932</v>
       </c>
-      <c r="AE10" s="2" t="n">
+      <c r="AE10" s="1" t="n">
         <v>0.704726829986932</v>
       </c>
-      <c r="AF10" s="2" t="n">
+      <c r="AF10" s="1" t="n">
         <v>0.704726829986932</v>
       </c>
-      <c r="AG10" s="2" t="n">
+      <c r="AG10" s="1" t="n">
         <v>0.482744456834738</v>
       </c>
-      <c r="AH10" s="2" t="n">
+      <c r="AH10" s="1" t="n">
         <v>0.482744456834738</v>
       </c>
-      <c r="AI10" s="2" t="n">
+      <c r="AI10" s="1" t="n">
         <v>0.503963918481622</v>
       </c>
-      <c r="AJ10" s="2" t="n">
+      <c r="AJ10" s="1" t="n">
         <v>0.503963918481622</v>
       </c>
-      <c r="AK10" s="2" t="n">
+      <c r="AK10" s="1" t="n">
         <v>0.503963918481622</v>
       </c>
-      <c r="AL10" s="2" t="n">
+      <c r="AL10" s="1" t="n">
         <v>0.503963918481622</v>
       </c>
-      <c r="AM10" s="2"/>
-      <c r="AO10" s="2" t="s">
+      <c r="AO10" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="AP10" s="2"/>
-      <c r="AQ10" s="2" t="n">
+      <c r="AP10" s="1"/>
+      <c r="AQ10" s="1" t="n">
         <v>0.0215443324970475</v>
       </c>
-      <c r="AR10" s="2" t="n">
+      <c r="AR10" s="1" t="n">
         <v>0.106265856096706</v>
       </c>
-      <c r="AS10" s="2" t="n">
+      <c r="AS10" s="1" t="n">
         <v>0.262074121009526</v>
       </c>
-      <c r="AT10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU10" s="2"/>
-      <c r="AV10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW10" s="2" t="n">
+      <c r="AT10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU10" s="1"/>
+      <c r="AV10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" s="1" t="n">
         <v>0.423672819588944</v>
       </c>
-      <c r="AX10" s="2"/>
+      <c r="AX10" s="1"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2" t="s">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1" t="s">
         <v>72</v>
       </c>
       <c r="C11" s="3" t="n">
@@ -1942,50 +1938,50 @@
       <c r="J11" s="3" t="n">
         <v>688129805.351454</v>
       </c>
-      <c r="K11" s="2" t="n">
+      <c r="K11" s="1" t="n">
         <v>0.755816001526835</v>
       </c>
-      <c r="L11" s="2" t="n">
+      <c r="L11" s="1" t="n">
         <v>0.755816001526835</v>
       </c>
-      <c r="M11" s="2" t="n">
+      <c r="M11" s="1" t="n">
         <v>0.755816001526835</v>
       </c>
-      <c r="N11" s="2" t="n">
+      <c r="N11" s="1" t="n">
         <v>0.755816001526835</v>
       </c>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" s="2" t="n">
+      <c r="O11" s="1"/>
+      <c r="P11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T11" s="2" t="s">
+      <c r="T11" s="1" t="s">
         <v>2</v>
       </c>
       <c r="U11" s="3" t="n">
         <v>135.292380130635</v>
       </c>
-      <c r="V11" s="2" t="n">
+      <c r="V11" s="1" t="n">
         <v>0.317873948745199</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>1546463193.02037</v>
-      </c>
-      <c r="X11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" s="2" t="s">
+        <v>9469904</v>
+      </c>
+      <c r="X11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="Z11" s="2" t="s">
+      <c r="Z11" s="1" t="s">
         <v>73</v>
       </c>
       <c r="AA11" s="3" t="n">
@@ -1994,65 +1990,64 @@
       <c r="AB11" s="3" t="n">
         <v>688129805.351454</v>
       </c>
-      <c r="AC11" s="2" t="n">
+      <c r="AC11" s="1" t="n">
         <v>0.755816001526835</v>
       </c>
-      <c r="AD11" s="2" t="n">
+      <c r="AD11" s="1" t="n">
         <v>0.755816001526835</v>
       </c>
-      <c r="AE11" s="2" t="n">
+      <c r="AE11" s="1" t="n">
         <v>0.755816001526835</v>
       </c>
-      <c r="AF11" s="2" t="n">
+      <c r="AF11" s="1" t="n">
         <v>0.755816001526835</v>
       </c>
-      <c r="AG11" s="2" t="n">
+      <c r="AG11" s="1" t="n">
         <v>0.527212896946081</v>
       </c>
-      <c r="AH11" s="2" t="n">
+      <c r="AH11" s="1" t="n">
         <v>0.527212896946081</v>
       </c>
-      <c r="AI11" s="2" t="n">
+      <c r="AI11" s="1" t="n">
         <v>0.552759720924687</v>
       </c>
-      <c r="AJ11" s="2" t="n">
+      <c r="AJ11" s="1" t="n">
         <v>0.552759720924687</v>
       </c>
-      <c r="AK11" s="2" t="n">
+      <c r="AK11" s="1" t="n">
         <v>0.552759720924687</v>
       </c>
-      <c r="AL11" s="2" t="n">
+      <c r="AL11" s="1" t="n">
         <v>0.552759720924687</v>
       </c>
-      <c r="AM11" s="2"/>
-      <c r="AO11" s="2" t="s">
+      <c r="AO11" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="AP11" s="2"/>
-      <c r="AQ11" s="2" t="n">
+      <c r="AP11" s="1"/>
+      <c r="AQ11" s="1" t="n">
         <v>0.0292864241091563</v>
       </c>
-      <c r="AR11" s="2" t="n">
+      <c r="AR11" s="1" t="n">
         <v>0.120592693201763</v>
       </c>
-      <c r="AS11" s="2" t="n">
+      <c r="AS11" s="1" t="n">
         <v>0.30929261554155</v>
       </c>
-      <c r="AT11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU11" s="2"/>
-      <c r="AV11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW11" s="2" t="n">
+      <c r="AT11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU11" s="1"/>
+      <c r="AV11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" s="1" t="n">
         <v>0.461536883148427</v>
       </c>
-      <c r="AX11" s="2"/>
+      <c r="AX11" s="1"/>
     </row>
-    <row r="12" customFormat="false" ht="52.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2" t="s">
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1" t="s">
         <v>74</v>
       </c>
       <c r="C12" s="3" t="n">
@@ -2079,50 +2074,50 @@
       <c r="J12" s="3" t="n">
         <v>994335664.087218</v>
       </c>
-      <c r="K12" s="2" t="n">
+      <c r="K12" s="1" t="n">
         <v>0.810608882557523</v>
       </c>
-      <c r="L12" s="2" t="n">
+      <c r="L12" s="1" t="n">
         <v>0.810608882557523</v>
       </c>
-      <c r="M12" s="2" t="n">
+      <c r="M12" s="1" t="n">
         <v>0.810608882557523</v>
       </c>
-      <c r="N12" s="2" t="n">
+      <c r="N12" s="1" t="n">
         <v>0.810608882557523</v>
       </c>
-      <c r="O12" s="2"/>
-      <c r="P12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="S12" s="2" t="n">
+      <c r="O12" s="1"/>
+      <c r="P12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T12" s="2" t="s">
+      <c r="T12" s="1" t="s">
         <v>2</v>
       </c>
       <c r="U12" s="3" t="n">
         <v>157.739334204581</v>
       </c>
-      <c r="V12" s="2" t="n">
+      <c r="V12" s="1" t="n">
         <v>0.393957078377362</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>1825093020.27926</v>
-      </c>
-      <c r="X12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="2" t="s">
+        <v>13130346</v>
+      </c>
+      <c r="X12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="Z12" s="2" t="s">
+      <c r="Z12" s="1" t="s">
         <v>75</v>
       </c>
       <c r="AA12" s="3" t="n">
@@ -2131,70 +2126,70 @@
       <c r="AB12" s="3" t="n">
         <v>994335664.087218</v>
       </c>
-      <c r="AC12" s="2" t="n">
+      <c r="AC12" s="1" t="n">
         <v>0.810608882557523</v>
       </c>
-      <c r="AD12" s="2" t="n">
+      <c r="AD12" s="1" t="n">
         <v>0.810608882557523</v>
       </c>
-      <c r="AE12" s="2" t="n">
+      <c r="AE12" s="1" t="n">
         <v>0.810608882557523</v>
       </c>
-      <c r="AF12" s="2" t="n">
+      <c r="AF12" s="1" t="n">
         <v>0.810608882557523</v>
       </c>
-      <c r="AG12" s="2" t="n">
+      <c r="AG12" s="1" t="n">
         <v>0.575777587439877</v>
       </c>
-      <c r="AH12" s="2" t="n">
+      <c r="AH12" s="1" t="n">
         <v>0.575777587439877</v>
       </c>
-      <c r="AI12" s="2" t="n">
+      <c r="AI12" s="1" t="n">
         <v>0.606280128143498</v>
       </c>
-      <c r="AJ12" s="2" t="n">
+      <c r="AJ12" s="1" t="n">
         <v>0.606280128143498</v>
       </c>
-      <c r="AK12" s="2" t="n">
+      <c r="AK12" s="1" t="n">
         <v>0.606280128143498</v>
       </c>
-      <c r="AL12" s="2" t="n">
+      <c r="AL12" s="1" t="n">
         <v>0.606280128143498</v>
       </c>
-      <c r="AM12" s="0" t="s">
+      <c r="AM12" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="AN12" s="0" t="n">
+      <c r="AN12" s="1" t="n">
         <v>0.15</v>
       </c>
-      <c r="AO12" s="2" t="s">
+      <c r="AO12" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="AP12" s="2"/>
-      <c r="AQ12" s="2" t="n">
+      <c r="AP12" s="1"/>
+      <c r="AQ12" s="1" t="n">
         <v>0.0398106851172534</v>
       </c>
-      <c r="AR12" s="2" t="n">
+      <c r="AR12" s="1" t="n">
         <v>0.13685108451411</v>
       </c>
-      <c r="AS12" s="2" t="n">
+      <c r="AS12" s="1" t="n">
         <v>0.36501857436376</v>
       </c>
-      <c r="AT12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU12" s="2"/>
-      <c r="AV12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW12" s="2" t="n">
+      <c r="AT12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU12" s="1"/>
+      <c r="AV12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" s="1" t="n">
         <v>0.502784895932285</v>
       </c>
-      <c r="AX12" s="2"/>
+      <c r="AX12" s="1"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2" t="s">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1" t="s">
         <v>77</v>
       </c>
       <c r="C13" s="3" t="n">
@@ -2221,50 +2216,50 @@
       <c r="J13" s="3" t="n">
         <v>1436797832.59904</v>
       </c>
-      <c r="K13" s="2" t="n">
+      <c r="K13" s="1" t="n">
         <v>0.86937397349853</v>
       </c>
-      <c r="L13" s="2" t="n">
+      <c r="L13" s="1" t="n">
         <v>0.86937397349853</v>
       </c>
-      <c r="M13" s="2" t="n">
+      <c r="M13" s="1" t="n">
         <v>0.86937397349853</v>
       </c>
-      <c r="N13" s="2" t="n">
+      <c r="N13" s="1" t="n">
         <v>0.86937397349853</v>
       </c>
-      <c r="O13" s="2"/>
-      <c r="P13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="S13" s="2" t="n">
+      <c r="O13" s="1"/>
+      <c r="P13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T13" s="2" t="s">
+      <c r="T13" s="1" t="s">
         <v>2</v>
       </c>
       <c r="U13" s="3" t="n">
         <v>183.910561195534</v>
       </c>
-      <c r="V13" s="2" t="n">
+      <c r="V13" s="1" t="n">
         <v>0.488250705086984</v>
       </c>
       <c r="W13" s="3" t="n">
-        <v>2153924223.80674</v>
-      </c>
-      <c r="X13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" s="2" t="s">
+        <v>18205676</v>
+      </c>
+      <c r="X13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="Z13" s="2" t="s">
+      <c r="Z13" s="1" t="s">
         <v>78</v>
       </c>
       <c r="AA13" s="3" t="n">
@@ -2273,65 +2268,64 @@
       <c r="AB13" s="3" t="n">
         <v>1436797832.59904</v>
       </c>
-      <c r="AC13" s="2" t="n">
+      <c r="AC13" s="1" t="n">
         <v>0.86937397349853</v>
       </c>
-      <c r="AD13" s="2" t="n">
+      <c r="AD13" s="1" t="n">
         <v>0.86937397349853</v>
       </c>
-      <c r="AE13" s="2" t="n">
+      <c r="AE13" s="1" t="n">
         <v>0.86937397349853</v>
       </c>
-      <c r="AF13" s="2" t="n">
+      <c r="AF13" s="1" t="n">
         <v>0.86937397349853</v>
       </c>
-      <c r="AG13" s="2" t="n">
+      <c r="AG13" s="1" t="n">
         <v>0.62881585810673</v>
       </c>
-      <c r="AH13" s="2" t="n">
+      <c r="AH13" s="1" t="n">
         <v>0.62881585810673</v>
       </c>
-      <c r="AI13" s="2" t="n">
+      <c r="AI13" s="1" t="n">
         <v>0.664982595270864</v>
       </c>
-      <c r="AJ13" s="2" t="n">
+      <c r="AJ13" s="1" t="n">
         <v>0.664982595270864</v>
       </c>
-      <c r="AK13" s="2" t="n">
+      <c r="AK13" s="1" t="n">
         <v>0.664982595270864</v>
       </c>
-      <c r="AL13" s="2" t="n">
+      <c r="AL13" s="1" t="n">
         <v>0.664982595270864</v>
       </c>
-      <c r="AM13" s="2"/>
-      <c r="AO13" s="2" t="s">
+      <c r="AO13" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="AP13" s="2"/>
-      <c r="AQ13" s="2" t="n">
+      <c r="AP13" s="1"/>
+      <c r="AQ13" s="1" t="n">
         <v>0.0541169056214547</v>
       </c>
-      <c r="AR13" s="2" t="n">
+      <c r="AR13" s="1" t="n">
         <v>0.155301443524061</v>
       </c>
-      <c r="AS13" s="2" t="n">
+      <c r="AS13" s="1" t="n">
         <v>0.430784806799414</v>
       </c>
-      <c r="AT13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU13" s="2"/>
-      <c r="AV13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW13" s="2" t="n">
+      <c r="AT13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU13" s="1"/>
+      <c r="AV13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" s="1" t="n">
         <v>0.54771928486665</v>
       </c>
-      <c r="AX13" s="2"/>
+      <c r="AX13" s="1"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2" t="s">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1" t="s">
         <v>79</v>
       </c>
       <c r="C14" s="3" t="n">
@@ -2358,50 +2352,50 @@
       <c r="J14" s="3" t="n">
         <v>2076148011.50311</v>
       </c>
-      <c r="K14" s="2" t="n">
+      <c r="K14" s="1" t="n">
         <v>0.932399239707306</v>
       </c>
-      <c r="L14" s="2" t="n">
+      <c r="L14" s="1" t="n">
         <v>0.932399239707306</v>
       </c>
-      <c r="M14" s="2" t="n">
+      <c r="M14" s="1" t="n">
         <v>0.932399239707306</v>
       </c>
-      <c r="N14" s="2" t="n">
+      <c r="N14" s="1" t="n">
         <v>0.932399239707306</v>
       </c>
-      <c r="O14" s="2"/>
-      <c r="P14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="S14" s="2" t="n">
+      <c r="O14" s="1"/>
+      <c r="P14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T14" s="2" t="s">
+      <c r="T14" s="1" t="s">
         <v>2</v>
       </c>
       <c r="U14" s="3" t="n">
         <v>214.423971609954</v>
       </c>
-      <c r="V14" s="2" t="n">
+      <c r="V14" s="1" t="n">
         <v>0.605113511349554</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>2542001700.92786</v>
-      </c>
-      <c r="X14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="2" t="s">
+        <v>25242794</v>
+      </c>
+      <c r="X14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="Z14" s="2" t="s">
+      <c r="Z14" s="1" t="s">
         <v>80</v>
       </c>
       <c r="AA14" s="3" t="n">
@@ -2410,70 +2404,70 @@
       <c r="AB14" s="3" t="n">
         <v>2076148011.50311</v>
       </c>
-      <c r="AC14" s="2" t="n">
+      <c r="AC14" s="1" t="n">
         <v>0.932399239707306</v>
       </c>
-      <c r="AD14" s="2" t="n">
+      <c r="AD14" s="1" t="n">
         <v>0.932399239707306</v>
       </c>
-      <c r="AE14" s="2" t="n">
+      <c r="AE14" s="1" t="n">
         <v>0.932399239707306</v>
       </c>
-      <c r="AF14" s="2" t="n">
+      <c r="AF14" s="1" t="n">
         <v>0.932399239707306</v>
       </c>
-      <c r="AG14" s="2" t="n">
+      <c r="AG14" s="1" t="n">
         <v>0.686739796810503</v>
       </c>
-      <c r="AH14" s="2" t="n">
+      <c r="AH14" s="1" t="n">
         <v>0.686739796810503</v>
       </c>
-      <c r="AI14" s="2" t="n">
+      <c r="AI14" s="1" t="n">
         <v>0.729368870075371</v>
       </c>
-      <c r="AJ14" s="2" t="n">
+      <c r="AJ14" s="1" t="n">
         <v>0.729368870075371</v>
       </c>
-      <c r="AK14" s="2" t="n">
+      <c r="AK14" s="1" t="n">
         <v>0.729368870075371</v>
       </c>
-      <c r="AL14" s="2" t="n">
+      <c r="AL14" s="1" t="n">
         <v>0.729368870075371</v>
       </c>
-      <c r="AM14" s="2" t="s">
+      <c r="AM14" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="AN14" s="0" t="n">
+      <c r="AN14" s="1" t="n">
         <v>0.18</v>
       </c>
-      <c r="AO14" s="2" t="s">
+      <c r="AO14" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="AP14" s="2"/>
-      <c r="AQ14" s="2" t="n">
+      <c r="AP14" s="1"/>
+      <c r="AQ14" s="1" t="n">
         <v>0.0735641565930299</v>
       </c>
-      <c r="AR14" s="2" t="n">
+      <c r="AR14" s="1" t="n">
         <v>0.176239292850986</v>
       </c>
-      <c r="AS14" s="2" t="n">
+      <c r="AS14" s="1" t="n">
         <v>0.508400291937672</v>
       </c>
-      <c r="AT14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU14" s="2"/>
-      <c r="AV14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW14" s="2" t="n">
+      <c r="AT14" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU14" s="1"/>
+      <c r="AV14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW14" s="1" t="n">
         <v>0.596669505074467</v>
       </c>
-      <c r="AX14" s="2"/>
+      <c r="AX14" s="1"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2" t="s">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1" t="s">
         <v>82</v>
       </c>
       <c r="C15" s="3" t="n">
@@ -2500,50 +2494,50 @@
       <c r="J15" s="3" t="n">
         <v>2999997959.2614</v>
       </c>
-      <c r="K15" s="2" t="n">
+      <c r="K15" s="1" t="n">
         <v>0.999993522589888</v>
       </c>
-      <c r="L15" s="2" t="n">
+      <c r="L15" s="1" t="n">
         <v>0.999993522589888</v>
       </c>
-      <c r="M15" s="2" t="n">
+      <c r="M15" s="1" t="n">
         <v>0.999993522589888</v>
       </c>
-      <c r="N15" s="2" t="n">
+      <c r="N15" s="1" t="n">
         <v>0.999993522589888</v>
       </c>
-      <c r="O15" s="2"/>
-      <c r="P15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="S15" s="2" t="n">
+      <c r="O15" s="1"/>
+      <c r="P15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S15" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T15" s="2" t="s">
+      <c r="T15" s="1" t="s">
         <v>2</v>
       </c>
       <c r="U15" s="3" t="n">
         <v>249.999996205237</v>
       </c>
-      <c r="V15" s="2" t="n">
+      <c r="V15" s="1" t="n">
         <v>0.749947430291069</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>2999999988.90395</v>
-      </c>
-      <c r="X15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="2" t="s">
+        <v>34999999</v>
+      </c>
+      <c r="X15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="Z15" s="2" t="s">
+      <c r="Z15" s="1" t="s">
         <v>83</v>
       </c>
       <c r="AA15" s="3" t="n">
@@ -2552,66 +2546,66 @@
       <c r="AB15" s="3" t="n">
         <v>2999997959.2614</v>
       </c>
-      <c r="AC15" s="2" t="n">
+      <c r="AC15" s="1" t="n">
         <v>0.999993522589888</v>
       </c>
-      <c r="AD15" s="2" t="n">
+      <c r="AD15" s="1" t="n">
         <v>0.999993522589888</v>
       </c>
-      <c r="AE15" s="2" t="n">
+      <c r="AE15" s="1" t="n">
         <v>0.999993522589888</v>
       </c>
-      <c r="AF15" s="2" t="n">
+      <c r="AF15" s="1" t="n">
         <v>0.999993522589888</v>
       </c>
-      <c r="AG15" s="2" t="n">
+      <c r="AG15" s="1" t="n">
         <v>0.74999945125952</v>
       </c>
-      <c r="AH15" s="2" t="n">
+      <c r="AH15" s="1" t="n">
         <v>0.74999945125952</v>
       </c>
-      <c r="AI15" s="2" t="n">
+      <c r="AI15" s="1" t="n">
         <v>0.799989281551548</v>
       </c>
-      <c r="AJ15" s="2" t="n">
+      <c r="AJ15" s="1" t="n">
         <v>0.799989281551548</v>
       </c>
-      <c r="AK15" s="2" t="n">
+      <c r="AK15" s="1" t="n">
         <v>0.799989281551548</v>
       </c>
-      <c r="AL15" s="2" t="n">
+      <c r="AL15" s="1" t="n">
         <v>0.799989281551548</v>
       </c>
       <c r="AM15" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="AN15" s="0" t="n">
+      <c r="AN15" s="1" t="n">
         <v>0.3</v>
       </c>
-      <c r="AO15" s="2" t="s">
+      <c r="AO15" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="AP15" s="2"/>
-      <c r="AQ15" s="2" t="n">
+      <c r="AP15" s="1"/>
+      <c r="AQ15" s="1" t="n">
         <v>0.0999998997189217</v>
       </c>
-      <c r="AR15" s="2" t="n">
+      <c r="AR15" s="1" t="n">
         <v>0.19999999768066</v>
       </c>
-      <c r="AS15" s="2" t="n">
+      <c r="AS15" s="1" t="n">
         <v>0.599999936772751</v>
       </c>
-      <c r="AT15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU15" s="2"/>
-      <c r="AV15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW15" s="2" t="n">
+      <c r="AT15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU15" s="1"/>
+      <c r="AV15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" s="1" t="n">
         <v>0.649994455412477</v>
       </c>
-      <c r="AX15" s="2"/>
+      <c r="AX15" s="1"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
